--- a/data.xlsx
+++ b/data.xlsx
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -28,19 +31,43 @@
     <t xml:space="preserve">age</t>
   </si>
   <si>
-    <t xml:space="preserve">Jane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex</t>
+    <t xml:space="preserve">score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
   </si>
 </sst>
 </file>
@@ -115,12 +142,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -247,55 +282,226 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="D7" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="C14" s="0" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>30</v>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
